--- a/template_files/zpay_template.xlsx
+++ b/template_files/zpay_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Varun\Desktop\Backup AutoRecons\Zomato Auto recons\template_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Varun\Desktop\Backup AutoRecons\Zomato Auto recons - Copy\template_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B58A92-EE24-4138-BA19-C5FB7C651E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4013AD-1734-499F-8340-5A1CFE79A6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="932" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Zpay Ads" sheetId="209" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Zomato Pay'!$A$1:$K$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Zomato Pay'!$A$1:$L$37</definedName>
     <definedName name="Summary">#REF!</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -775,7 +775,7 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -891,9 +891,6 @@
     <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -941,6 +938,12 @@
     </xf>
     <xf numFmtId="49" fontId="26" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="24" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1026,7 +1029,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>1108364</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>80819</xdr:rowOff>
@@ -1266,107 +1269,111 @@
   <sheetPr codeName="Sheet66">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:T1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="8" width="15.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" style="1" customWidth="1"/>
-    <col min="10" max="11" width="11" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="14.44140625" style="1"/>
+    <col min="4" max="9" width="15.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="11" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="14.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="11"/>
-      <c r="S1" s="12"/>
-    </row>
-    <row r="2" spans="2:19" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="71" t="s">
+    <row r="1" spans="2:20" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="11"/>
+      <c r="T1" s="12"/>
+    </row>
+    <row r="2" spans="2:20" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="11"/>
-    </row>
-    <row r="3" spans="2:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D3" s="13"/>
     </row>
-    <row r="4" spans="2:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="73" t="s">
+    <row r="4" spans="2:20" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="79" t="s">
+      <c r="C4" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
       <c r="I4" s="81"/>
-      <c r="J4" s="77" t="s">
+      <c r="J4" s="82"/>
+      <c r="K4" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="14"/>
-    </row>
-    <row r="5" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="74"/>
-      <c r="C5" s="76"/>
+      <c r="L4" s="14"/>
+    </row>
+    <row r="5" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="75"/>
+      <c r="C5" s="77"/>
       <c r="D5" s="9"/>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="8"/>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="78"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="1" t="s">
+      <c r="K5" s="79"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="66">
+      <c r="N5" s="65">
         <f>D6</f>
         <v>0</v>
       </c>
-      <c r="N5" s="66">
+      <c r="O5" s="65">
         <f>E6</f>
         <v>0</v>
       </c>
-      <c r="O5" s="66">
+      <c r="P5" s="65">
         <f>F6</f>
         <v>0</v>
       </c>
-      <c r="P5" s="66">
+      <c r="Q5" s="65">
         <f>G6</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="66">
+      <c r="R5" s="65">
         <f>H6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="70">
+    <row r="6" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="71">
         <v>1</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -1377,41 +1384,42 @@
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="18">
-        <f t="shared" ref="I6:I14" si="0">SUM(D6:H6)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="19" t="e">
-        <f>I6/$I$12</f>
+      <c r="I6" s="38"/>
+      <c r="J6" s="18">
+        <f t="shared" ref="J6:J14" si="0">SUM(D6:I6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="19" t="e">
+        <f>J6/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K6" s="20"/>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="20"/>
+      <c r="M6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="66">
+      <c r="N6" s="65">
         <f>D12</f>
         <v>0</v>
       </c>
-      <c r="N6" s="66">
+      <c r="O6" s="65">
         <f>E12</f>
         <v>0</v>
       </c>
-      <c r="O6" s="66">
+      <c r="P6" s="65">
         <f>F12</f>
         <v>0</v>
       </c>
-      <c r="P6" s="66">
+      <c r="Q6" s="65">
         <f>G12</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="66">
+      <c r="R6" s="65">
         <f>H12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="68"/>
+    <row r="7" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="69"/>
       <c r="C7" s="21" t="s">
         <v>15</v>
       </c>
@@ -1420,41 +1428,42 @@
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
-      <c r="I7" s="18">
+      <c r="I7" s="66"/>
+      <c r="J7" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="23" t="e">
-        <f>-I7/I12</f>
+      <c r="K7" s="23" t="e">
+        <f>-J7/J12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="24"/>
+      <c r="M7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="66">
-        <f t="shared" ref="M7:Q8" si="1">D17</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="66">
+      <c r="N7" s="65">
+        <f t="shared" ref="N7:R8" si="1">D17</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O7" s="66">
+      <c r="P7" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P7" s="66">
+      <c r="Q7" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="R7" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="68"/>
+    <row r="8" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="69"/>
       <c r="C8" s="21" t="s">
         <v>21</v>
       </c>
@@ -1473,41 +1482,44 @@
       <c r="H8" s="28">
         <v>0</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="28">
+        <v>0</v>
+      </c>
+      <c r="J8" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="19" t="e">
-        <f>I8/$I$12</f>
+      <c r="K8" s="19" t="e">
+        <f>J8/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K8" s="20"/>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="20"/>
+      <c r="M8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="66">
+      <c r="N8" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N8" s="66">
+      <c r="O8" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O8" s="66">
+      <c r="P8" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P8" s="66">
+      <c r="Q8" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q8" s="66">
+      <c r="R8" s="65">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="68"/>
+    <row r="9" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="69"/>
       <c r="C9" s="15" t="s">
         <v>14</v>
       </c>
@@ -1532,40 +1544,44 @@
         <v>0</v>
       </c>
       <c r="I9" s="18">
+        <f t="shared" ref="I9" si="3">I6+I7+I8</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="19" t="e">
-        <f>I9/$I$12</f>
+      <c r="K9" s="19" t="e">
+        <f>J9/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="20"/>
+      <c r="M9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="66">
+      <c r="N9" s="65">
         <f>-D7</f>
         <v>0</v>
       </c>
-      <c r="N9" s="66">
+      <c r="O9" s="65">
         <f>-E7</f>
         <v>0</v>
       </c>
-      <c r="O9" s="66">
+      <c r="P9" s="65">
         <f>-F7</f>
         <v>0</v>
       </c>
-      <c r="P9" s="66">
+      <c r="Q9" s="65">
         <f>-G7</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="66">
+      <c r="R9" s="65">
         <f>-H7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B10" s="68"/>
+    <row r="10" spans="2:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="69"/>
       <c r="C10" s="21" t="s">
         <v>25</v>
       </c>
@@ -1582,25 +1598,29 @@
         <v>0</v>
       </c>
       <c r="G10" s="31">
-        <f t="shared" ref="G10:H10" si="3">G9*5%</f>
+        <f t="shared" ref="G10:H10" si="4">G9*5%</f>
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" ref="I10" si="5">I9*5%</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="19" t="e">
-        <f>I10/$I$12</f>
+      <c r="K10" s="19" t="e">
+        <f>J10/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11" spans="2:19" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B11" s="68"/>
+      <c r="L10" s="20"/>
+    </row>
+    <row r="11" spans="2:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B11" s="69"/>
       <c r="C11" s="21" t="s">
         <v>26</v>
       </c>
@@ -1609,18 +1629,19 @@
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
-      <c r="I11" s="18">
+      <c r="I11" s="66"/>
+      <c r="J11" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="19" t="e">
-        <f>I11/I12</f>
+      <c r="K11" s="19" t="e">
+        <f>J11/J12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="68"/>
+      <c r="L11" s="20"/>
+    </row>
+    <row r="12" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="69"/>
       <c r="C12" s="15" t="s">
         <v>17</v>
       </c>
@@ -1633,28 +1654,32 @@
         <v>0</v>
       </c>
       <c r="F12" s="26">
-        <f t="shared" ref="F12:H12" si="4">F9+F10+F11</f>
+        <f t="shared" ref="F12:I12" si="6">F9+F10+F11</f>
         <v>0</v>
       </c>
       <c r="G12" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H12" s="28">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="28">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="19" t="e">
-        <f>I12/$I$12</f>
+      <c r="K12" s="19" t="e">
+        <f>J12/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="20"/>
+    </row>
+    <row r="13" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="34"/>
       <c r="C13" s="35" t="s">
         <v>8</v>
@@ -1664,52 +1689,57 @@
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
-      <c r="I13" s="18">
+      <c r="I13" s="66"/>
+      <c r="J13" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="19" t="e">
-        <f>I13/I12</f>
+      <c r="K13" s="19" t="e">
+        <f>J13/J12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="34"/>
       <c r="C14" s="36" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="37">
-        <f t="shared" ref="D14:H14" si="5">D13-D12</f>
+        <f t="shared" ref="D14:I14" si="7">D13-D12</f>
         <v>0</v>
       </c>
       <c r="E14" s="38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F14" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G14" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H14" s="39">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="39">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="19" t="e">
-        <f>I14/I12</f>
+      <c r="K14" s="19" t="e">
+        <f>J14/J12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="20"/>
+    </row>
+    <row r="15" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="40"/>
       <c r="C15" s="21"/>
       <c r="D15" s="22"/>
@@ -1717,12 +1747,13 @@
       <c r="F15" s="33"/>
       <c r="G15" s="31"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="24"/>
-    </row>
-    <row r="16" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="67">
+      <c r="I15" s="3"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="24"/>
+    </row>
+    <row r="16" spans="2:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="68">
         <v>2</v>
       </c>
       <c r="C16" s="15" t="s">
@@ -1733,12 +1764,13 @@
       <c r="F16" s="26"/>
       <c r="G16" s="27"/>
       <c r="H16" s="28"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="68"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="69"/>
       <c r="C17" s="21" t="s">
         <v>10</v>
       </c>
@@ -1747,18 +1779,19 @@
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
-      <c r="I17" s="18">
-        <f>SUM(D17:H17)</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="19" t="e">
-        <f>I17/$I$12</f>
+      <c r="I17" s="66"/>
+      <c r="J17" s="18">
+        <f>SUM(D17:I17)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="19" t="e">
+        <f>J17/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K17" s="20"/>
-    </row>
-    <row r="18" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="68"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="69"/>
       <c r="C18" s="42" t="s">
         <v>22</v>
       </c>
@@ -1767,65 +1800,71 @@
       <c r="F18" s="43"/>
       <c r="G18" s="43"/>
       <c r="H18" s="43"/>
-      <c r="I18" s="18">
-        <f>SUM(D18:H18)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="19" t="e">
-        <f>I18/I12</f>
+      <c r="I18" s="44"/>
+      <c r="J18" s="18">
+        <f>SUM(D18:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="19" t="e">
+        <f>J18/J12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="68"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="69"/>
       <c r="C19" s="15" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="27">
-        <f t="shared" ref="D19:H19" si="6">SUM(D17:D18)</f>
+        <f t="shared" ref="D19:I19" si="8">SUM(D17:D18)</f>
         <v>0</v>
       </c>
       <c r="E19" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F19" s="26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G19" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H19" s="28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="18">
-        <f>SUM(D19:H19)</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="19" t="e">
-        <f>I19/$I$12</f>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="28">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="18">
+        <f>SUM(D19:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="19" t="e">
+        <f>J19/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="64"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="63"/>
       <c r="C20" s="15"/>
       <c r="D20" s="16"/>
       <c r="E20" s="25"/>
       <c r="F20" s="26"/>
       <c r="G20" s="27"/>
       <c r="H20" s="28"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="67">
+      <c r="I20" s="28"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="68">
         <v>3</v>
       </c>
       <c r="C21" s="15" t="s">
@@ -1836,12 +1875,13 @@
       <c r="F21" s="33"/>
       <c r="G21" s="31"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="24"/>
-    </row>
-    <row r="22" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="68"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="24"/>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="69"/>
       <c r="C22" s="21" t="s">
         <v>18</v>
       </c>
@@ -1860,18 +1900,21 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="18">
-        <f>SUM(D22:H22)</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="19" t="e">
-        <f t="shared" ref="J22:J24" si="7">I22/$I$12</f>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="18">
+        <f>SUM(D22:I22)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="19" t="e">
+        <f t="shared" ref="K22:K24" si="9">J22/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K22" s="24"/>
-    </row>
-    <row r="23" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="68"/>
+      <c r="L22" s="24"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="69"/>
       <c r="C23" s="21" t="s">
         <v>19</v>
       </c>
@@ -1890,52 +1933,59 @@
       <c r="H23" s="4">
         <v>0</v>
       </c>
-      <c r="I23" s="18">
-        <f>SUM(D23:H23)</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="19" t="e">
-        <f t="shared" si="7"/>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23" s="18">
+        <f>SUM(D23:I23)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="19" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="24"/>
-    </row>
-    <row r="24" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="68"/>
+      <c r="L23" s="24"/>
+    </row>
+    <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="69"/>
       <c r="C24" s="15" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="27">
-        <f t="shared" ref="D24:H24" si="8">SUM(D22:D23)</f>
+        <f t="shared" ref="D24:H24" si="10">SUM(D22:D23)</f>
         <v>0</v>
       </c>
       <c r="E24" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F24" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G24" s="25">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="45">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="18">
-        <f>SUM(D24:H24)</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="19" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="67">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="67">
+        <f t="shared" ref="I24" si="11">SUM(I22:I23)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="18">
+        <f>SUM(D24:I24)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="19" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K24" s="24"/>
-    </row>
-    <row r="25" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="34"/>
       <c r="C25" s="15"/>
       <c r="D25" s="16"/>
@@ -1943,12 +1993,13 @@
       <c r="F25" s="33"/>
       <c r="G25" s="31"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="24"/>
-    </row>
-    <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="67">
+      <c r="I25" s="3"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="68">
         <v>4</v>
       </c>
       <c r="C26" s="21" t="s">
@@ -1963,119 +2014,132 @@
         <v>0</v>
       </c>
       <c r="F26" s="33">
-        <f t="shared" ref="F26:H26" si="9">F12-F19+F24</f>
+        <f t="shared" ref="F26:H26" si="12">F12-F19+F24</f>
         <v>0</v>
       </c>
       <c r="G26" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H26" s="31">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
-        <f>SUM(D26:H26)</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="19" t="e">
-        <f t="shared" ref="J26:J28" si="10">I26/$I$12</f>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="31">
+        <f t="shared" ref="I26" si="13">I12-I19+I24</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="18">
+        <f>SUM(D26:I26)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="19" t="e">
+        <f t="shared" ref="K26:K28" si="14">J26/$J$12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="20"/>
-    </row>
-    <row r="27" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="68"/>
+      <c r="L26" s="20"/>
+    </row>
+    <row r="27" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="69"/>
       <c r="C27" s="21" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="22">
         <v>0</v>
       </c>
-      <c r="E27" s="46">
-        <v>0</v>
-      </c>
-      <c r="F27" s="47">
-        <v>0</v>
-      </c>
-      <c r="G27" s="48">
-        <v>0</v>
-      </c>
-      <c r="H27" s="49">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <f>SUM(D27:H27)</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="19" t="e">
-        <f t="shared" si="10"/>
+      <c r="E27" s="45">
+        <v>0</v>
+      </c>
+      <c r="F27" s="46">
+        <v>0</v>
+      </c>
+      <c r="G27" s="47">
+        <v>0</v>
+      </c>
+      <c r="H27" s="48">
+        <v>0</v>
+      </c>
+      <c r="I27" s="48">
+        <v>0</v>
+      </c>
+      <c r="J27" s="18">
+        <f>SUM(D27:I27)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="19" t="e">
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="20"/>
-      <c r="L27" s="50"/>
-    </row>
-    <row r="28" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="69"/>
-      <c r="C28" s="51" t="s">
+      <c r="L27" s="20"/>
+      <c r="M27" s="49"/>
+    </row>
+    <row r="28" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="70"/>
+      <c r="C28" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="51">
         <f>D27-D26</f>
         <v>0</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="52">
         <f>E27-E26</f>
         <v>0</v>
       </c>
-      <c r="F28" s="54">
-        <f t="shared" ref="F28:H28" si="11">F27-F26</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="52">
-        <f t="shared" si="11"/>
+      <c r="F28" s="53">
+        <f t="shared" ref="F28:H28" si="15">F27-F26</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="51">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H28" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="55">
-        <f>SUM(D28:H28)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="56" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" ref="I28" si="16">I27-I26</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="54">
+        <f>SUM(D28:I28)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="55" t="e">
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="20"/>
-    </row>
-    <row r="29" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="57"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="20"/>
+      <c r="L28" s="20"/>
+    </row>
+    <row r="29" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="56"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
       <c r="K29" s="20"/>
-    </row>
-    <row r="30" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L29" s="20"/>
+    </row>
+    <row r="30" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
       <c r="I30" s="60"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="60"/>
-    </row>
-    <row r="31" spans="1:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+    </row>
+    <row r="31" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>24</v>
       </c>
@@ -2085,26 +2149,28 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="60"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="60"/>
-    </row>
-    <row r="32" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I31" s="2"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="59"/>
+    </row>
+    <row r="32" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="60"/>
-    </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="59"/>
+    </row>
+    <row r="33" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2117,43 +2183,46 @@
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
-      <c r="K33" s="60"/>
-    </row>
-    <row r="34" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="60"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="60"/>
-    </row>
-    <row r="35" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="60"/>
-      <c r="J35" s="60"/>
-      <c r="K35" s="60"/>
-    </row>
-    <row r="36" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="59"/>
+    </row>
+    <row r="34" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="59"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="59"/>
+    </row>
+    <row r="35" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="59"/>
+    </row>
+    <row r="36" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3112,12 +3181,12 @@
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B6:B12"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:K2"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="D4:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="72" orientation="landscape" r:id="rId1"/>
